--- a/asx_eod_output/Report_XLSX/Report_20260814.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260814.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.535</v>
+        <v>1.537</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-2.41%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>235132.83</v>
+        <v>235439.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-6127.24</v>
+        <v>-5820.88</v>
       </c>
     </row>
     <row r="5">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>61.07</v>
+        <v>61.02</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2.38</v>
+        <v>-2.43</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>675739.55</v>
+        <v>675186.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-26334.7</v>
+        <v>-26887.95</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>169.3</v>
+        <v>169</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>136.89</v>
+        <v>137.02</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>547560</v>
+        <v>548080</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2520</v>
+        <v>-2000</v>
       </c>
     </row>
     <row r="12">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.5</v>
+        <v>35.46</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1749186.83</v>
+        <v>1749459.95</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-35543.2</v>
+        <v>-35270.09</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260814.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260814.xlsx
@@ -488,24 +488,24 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.537</v>
+        <v>1.535</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.038</v>
+        <v>-0.04</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
         <v>153181</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>235439.2</v>
+        <v>235132.83</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-5820.88</v>
+        <v>-6127.24</v>
       </c>
     </row>
     <row r="5">
@@ -515,24 +515,24 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
         <v>70000</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>163800</v>
+        <v>163100</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -542,24 +542,24 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
         <v>57458</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>68949.60000000001</v>
+        <v>70098.75999999999</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1149.16</v>
       </c>
     </row>
     <row r="7">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>61.02</v>
+        <v>61.35</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-2.43</v>
+        <v>-2.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
         <v>11065</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>675186.3</v>
+        <v>678837.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-26887.95</v>
+        <v>-23236.5</v>
       </c>
     </row>
     <row r="8">
@@ -623,14 +623,14 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>169</v>
+        <v>167.17</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0</v>
+        <v>-1.83</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-1.08%</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -650,24 +650,24 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.86</v>
+        <v>0.865</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.035</v>
+        <v>-0.03</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8600</v>
+        <v>8650</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-350</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="11">
@@ -677,24 +677,24 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>137.02</v>
+        <v>136.5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1.02</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
         <v>4000</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>548080</v>
+        <v>546000</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2000</v>
+        <v>-4080</v>
       </c>
     </row>
     <row r="12">
@@ -704,24 +704,24 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.88%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
         <v>20000</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5400</v>
+        <v>5200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -758,24 +758,24 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
         <v>9412</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1176.5</v>
+        <v>1129.44</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>47.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -785,24 +785,24 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-4.76%</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16">
@@ -812,14 +812,14 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>35.46</v>
+        <v>35.37</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.33</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -839,24 +839,24 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>32.66</v>
+        <v>32.6</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
         <v>1288</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>42066.08</v>
+        <v>41988.8</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>141.68</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1749459.95</v>
+        <v>1750869.85</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-35270.09</v>
+        <v>-33860.18</v>
       </c>
     </row>
   </sheetData>

--- a/asx_eod_output/Report_XLSX/Report_20260814.xlsx
+++ b/asx_eod_output/Report_XLSX/Report_20260814.xlsx
@@ -731,24 +731,24 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
         <v>700000</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -870,10 +870,10 @@
       <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="8" t="n">
-        <v>1750869.85</v>
+        <v>1752269.85</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>-33860.18</v>
+        <v>-32460.18</v>
       </c>
     </row>
   </sheetData>
